--- a/Data/nfl_draft_value_charts.xlsx
+++ b/Data/nfl_draft_value_charts.xlsx
@@ -1,22 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="20225"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11122"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Joe/Documents/5. Columbia (2024-2026)/Git Repos/draft_pick_value/Data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC5A5E2E-6C96-4D41-967A-463B13530413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="0" windowWidth="24220" windowHeight="17560" tabRatio="500"/>
+    <workbookView xWindow="1360" yWindow="760" windowWidth="24220" windowHeight="17560" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DVC_New" sheetId="4" r:id="rId1"/>
     <sheet name="DVC_Original" sheetId="6" r:id="rId2"/>
+    <sheet name="DVC_New_Raw" sheetId="9" r:id="rId3"/>
+    <sheet name="DVC_Original_Raw" sheetId="10" r:id="rId4"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId3"/>
+    <externalReference r:id="rId5"/>
   </externalReferences>
   <definedNames>
     <definedName name="lkpCopyright">[1]lkpTables!$J$6</definedName>
   </definedNames>
-  <calcPr calcId="140001" concurrentCalc="0"/>
+  <calcPr calcId="140001"/>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
@@ -26,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="16">
   <si>
     <t>Round 1</t>
   </si>
@@ -69,15 +77,21 @@
   <si>
     <t>Original created by Jimmy Johnson for the Dallas Cowboys.</t>
   </si>
+  <si>
+    <t>pick</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -115,46 +129,66 @@
       <sz val="12"/>
       <color theme="0" tint="-0.499984740745262"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="0" tint="-0.499984740745262"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1" tint="0.499984740745262"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1" tint="0.499984740745262"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="18"/>
       <color theme="1" tint="0.499984740745262"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <color theme="1" tint="0.499984740745262"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="18"/>
       <color theme="1" tint="0.499984740745262"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF808080"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -406,7 +440,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -423,13 +457,13 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -450,7 +484,7 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -458,23 +492,23 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="89" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="89" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -489,6 +523,17 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="106">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
@@ -600,6 +645,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -622,6 +675,11 @@
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Picture 2">
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
@@ -673,6 +731,11 @@
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Picture 1">
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
@@ -706,7 +769,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Draft_Board"/>
@@ -1049,12 +1112,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr enableFormatConditionsCalculation="0">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="6.83203125" style="1" customWidth="1"/>
@@ -1074,7 +1137,7 @@
     <col min="16" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="17" customFormat="1" ht="36" customHeight="1">
+    <row r="1" spans="1:15" s="17" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="18"/>
       <c r="B1" s="21"/>
       <c r="C1" s="18"/>
@@ -1095,8 +1158,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="6" customHeight="1" thickBot="1"/>
-    <row r="3" spans="1:15" ht="22" customHeight="1">
+    <row r="2" spans="1:15" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="28" t="s">
         <v>0</v>
       </c>
@@ -1126,7 +1189,7 @@
       </c>
       <c r="O3" s="27"/>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B4" s="5">
         <v>1</v>
       </c>
@@ -1170,7 +1233,7 @@
         <v>43.5</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B5" s="5">
         <v>2</v>
       </c>
@@ -1214,7 +1277,7 @@
         <v>43.1</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="5">
         <v>3</v>
       </c>
@@ -1258,7 +1321,7 @@
         <v>42.6</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B7" s="5">
         <v>4</v>
       </c>
@@ -1302,7 +1365,7 @@
         <v>42.2</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B8" s="5">
         <v>5</v>
       </c>
@@ -1346,7 +1409,7 @@
         <v>41.8</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B9" s="5">
         <v>6</v>
       </c>
@@ -1390,7 +1453,7 @@
         <v>41.4</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B10" s="5">
         <v>7</v>
       </c>
@@ -1434,7 +1497,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B11" s="5">
         <v>8</v>
       </c>
@@ -1478,7 +1541,7 @@
         <v>40.6</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B12" s="5">
         <v>9</v>
       </c>
@@ -1522,7 +1585,7 @@
         <v>40.200000000000003</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B13" s="5">
         <v>10</v>
       </c>
@@ -1566,7 +1629,7 @@
         <v>39.799999999999997</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B14" s="5">
         <v>11</v>
       </c>
@@ -1610,7 +1673,7 @@
         <v>39.4</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B15" s="5">
         <v>12</v>
       </c>
@@ -1654,7 +1717,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B16" s="5">
         <v>13</v>
       </c>
@@ -1698,7 +1761,7 @@
         <v>38.6</v>
       </c>
     </row>
-    <row r="17" spans="2:15">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B17" s="5">
         <v>14</v>
       </c>
@@ -1742,7 +1805,7 @@
         <v>38.200000000000003</v>
       </c>
     </row>
-    <row r="18" spans="2:15">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B18" s="5">
         <v>15</v>
       </c>
@@ -1786,7 +1849,7 @@
         <v>37.799999999999997</v>
       </c>
     </row>
-    <row r="19" spans="2:15">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B19" s="5">
         <v>16</v>
       </c>
@@ -1830,7 +1893,7 @@
         <v>37.4</v>
       </c>
     </row>
-    <row r="20" spans="2:15">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B20" s="5">
         <v>17</v>
       </c>
@@ -1874,7 +1937,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="2:15">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B21" s="5">
         <v>18</v>
       </c>
@@ -1918,7 +1981,7 @@
         <v>36.6</v>
       </c>
     </row>
-    <row r="22" spans="2:15">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B22" s="5">
         <v>19</v>
       </c>
@@ -1962,7 +2025,7 @@
         <v>36.299999999999997</v>
       </c>
     </row>
-    <row r="23" spans="2:15">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B23" s="5">
         <v>20</v>
       </c>
@@ -2006,7 +2069,7 @@
         <v>35.9</v>
       </c>
     </row>
-    <row r="24" spans="2:15">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B24" s="5">
         <v>21</v>
       </c>
@@ -2050,7 +2113,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="25" spans="2:15">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B25" s="5">
         <v>22</v>
       </c>
@@ -2094,7 +2157,7 @@
         <v>35.1</v>
       </c>
     </row>
-    <row r="26" spans="2:15">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B26" s="5">
         <v>23</v>
       </c>
@@ -2138,7 +2201,7 @@
         <v>43.5</v>
       </c>
     </row>
-    <row r="27" spans="2:15">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B27" s="5">
         <v>24</v>
       </c>
@@ -2182,7 +2245,7 @@
         <v>43.1</v>
       </c>
     </row>
-    <row r="28" spans="2:15">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B28" s="5">
         <v>25</v>
       </c>
@@ -2226,7 +2289,7 @@
         <v>42.6</v>
       </c>
     </row>
-    <row r="29" spans="2:15">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B29" s="5">
         <v>26</v>
       </c>
@@ -2270,7 +2333,7 @@
         <v>42.2</v>
       </c>
     </row>
-    <row r="30" spans="2:15">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B30" s="5">
         <v>27</v>
       </c>
@@ -2314,7 +2377,7 @@
         <v>41.8</v>
       </c>
     </row>
-    <row r="31" spans="2:15">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B31" s="5">
         <v>28</v>
       </c>
@@ -2358,7 +2421,7 @@
         <v>41.4</v>
       </c>
     </row>
-    <row r="32" spans="2:15">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B32" s="5">
         <v>29</v>
       </c>
@@ -2402,7 +2465,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="2:15">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B33" s="5">
         <v>30</v>
       </c>
@@ -2446,7 +2509,7 @@
         <v>40.6</v>
       </c>
     </row>
-    <row r="34" spans="2:15">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B34" s="5">
         <v>31</v>
       </c>
@@ -2490,7 +2553,7 @@
         <v>40.200000000000003</v>
       </c>
     </row>
-    <row r="35" spans="2:15" ht="16" thickBot="1">
+    <row r="35" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B35" s="10">
         <v>32</v>
       </c>
@@ -2534,7 +2597,7 @@
         <v>39.799999999999997</v>
       </c>
     </row>
-    <row r="37" spans="2:15">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="3" t="s">
         <v>8</v>
       </c>
@@ -2542,12 +2605,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="2:15">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="2:15">
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B40" s="4"/>
     </row>
   </sheetData>
@@ -2562,9 +2625,9 @@
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="O1" r:id="rId1"/>
-    <hyperlink ref="M1" r:id="rId2" display="http://www.fantasycube.com"/>
-    <hyperlink ref="N1" r:id="rId3" display="http://www.fantasycube.com"/>
+    <hyperlink ref="O1" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="M1" r:id="rId2" display="http://www.fantasycube.com" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="N1" r:id="rId3" display="http://www.fantasycube.com" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.75000000000000011" right="0.75000000000000011" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup scale="74" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
@@ -2578,12 +2641,12 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr enableFormatConditionsCalculation="0">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="6.83203125" style="1" customWidth="1"/>
@@ -2603,7 +2666,7 @@
     <col min="16" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="17" customFormat="1" ht="36" customHeight="1">
+    <row r="1" spans="1:15" s="17" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="18"/>
       <c r="B1" s="21"/>
       <c r="C1" s="18"/>
@@ -2624,8 +2687,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="6" customHeight="1" thickBot="1"/>
-    <row r="3" spans="1:15" ht="22" customHeight="1">
+    <row r="2" spans="1:15" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="28" t="s">
         <v>0</v>
       </c>
@@ -2655,7 +2718,7 @@
       </c>
       <c r="O3" s="27"/>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B4" s="5">
         <v>1</v>
       </c>
@@ -2699,7 +2762,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B5" s="5">
         <v>2</v>
       </c>
@@ -2743,7 +2806,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="5">
         <v>3</v>
       </c>
@@ -2787,7 +2850,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B7" s="5">
         <v>4</v>
       </c>
@@ -2831,7 +2894,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B8" s="5">
         <v>5</v>
       </c>
@@ -2875,7 +2938,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B9" s="5">
         <v>6</v>
       </c>
@@ -2919,7 +2982,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B10" s="5">
         <v>7</v>
       </c>
@@ -2963,7 +3026,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B11" s="5">
         <v>8</v>
       </c>
@@ -3007,7 +3070,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B12" s="5">
         <v>9</v>
       </c>
@@ -3051,7 +3114,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B13" s="5">
         <v>10</v>
       </c>
@@ -3095,7 +3158,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B14" s="5">
         <v>11</v>
       </c>
@@ -3139,7 +3202,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B15" s="5">
         <v>12</v>
       </c>
@@ -3183,7 +3246,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B16" s="5">
         <v>13</v>
       </c>
@@ -3227,7 +3290,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="17" spans="2:15">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B17" s="5">
         <v>14</v>
       </c>
@@ -3271,7 +3334,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="2:15">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B18" s="5">
         <v>15</v>
       </c>
@@ -3315,7 +3378,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="19" spans="2:15">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B19" s="5">
         <v>16</v>
       </c>
@@ -3359,7 +3422,7 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="20" spans="2:15">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B20" s="5">
         <v>17</v>
       </c>
@@ -3403,7 +3466,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="21" spans="2:15">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B21" s="5">
         <v>18</v>
       </c>
@@ -3447,7 +3510,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="22" spans="2:15">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B22" s="5">
         <v>19</v>
       </c>
@@ -3491,7 +3554,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="2:15">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B23" s="5">
         <v>20</v>
       </c>
@@ -3535,7 +3598,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="24" spans="2:15">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B24" s="5">
         <v>21</v>
       </c>
@@ -3579,7 +3642,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="25" spans="2:15">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B25" s="5">
         <v>22</v>
       </c>
@@ -3623,7 +3686,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="26" spans="2:15">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B26" s="5">
         <v>23</v>
       </c>
@@ -3667,7 +3730,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="27" spans="2:15">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B27" s="5">
         <v>24</v>
       </c>
@@ -3711,7 +3774,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="2:15">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B28" s="5">
         <v>25</v>
       </c>
@@ -3755,7 +3818,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="29" spans="2:15">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B29" s="5">
         <v>26</v>
       </c>
@@ -3799,7 +3862,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="30" spans="2:15">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B30" s="5">
         <v>27</v>
       </c>
@@ -3843,7 +3906,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="31" spans="2:15">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B31" s="5">
         <v>28</v>
       </c>
@@ -3887,7 +3950,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="32" spans="2:15">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B32" s="5">
         <v>29</v>
       </c>
@@ -3931,7 +3994,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="2:15">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B33" s="5">
         <v>30</v>
       </c>
@@ -3975,7 +4038,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="34" spans="2:15">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B34" s="5">
         <v>31</v>
       </c>
@@ -4019,7 +4082,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="35" spans="2:15" ht="16" thickBot="1">
+    <row r="35" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B35" s="10">
         <v>32</v>
       </c>
@@ -4063,16 +4126,16 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="2:15">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C37" s="2"/>
     </row>
-    <row r="38" spans="2:15">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="2"/>
     </row>
-    <row r="40" spans="2:15">
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B40" s="4"/>
     </row>
   </sheetData>
@@ -4087,9 +4150,9 @@
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="O1" r:id="rId1"/>
-    <hyperlink ref="M1" r:id="rId2" display="http://www.fantasycube.com"/>
-    <hyperlink ref="N1" r:id="rId3" display="http://www.fantasycube.com"/>
+    <hyperlink ref="O1" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="M1" r:id="rId2" display="http://www.fantasycube.com" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="N1" r:id="rId3" display="http://www.fantasycube.com" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.75000000000000011" right="0.75000000000000011" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup scale="74" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
@@ -4100,4 +4163,4363 @@
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50A06F35-04AD-3846-8207-E5494D8F6795}">
+  <dimension ref="A1:B271"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="10.83203125" style="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="33" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="31">
+        <v>1</v>
+      </c>
+      <c r="B2" s="32">
+        <v>494.6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="31">
+        <v>2</v>
+      </c>
+      <c r="B3" s="32">
+        <v>435.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="31">
+        <v>3</v>
+      </c>
+      <c r="B4" s="32">
+        <v>401.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="31">
+        <v>4</v>
+      </c>
+      <c r="B5" s="32">
+        <v>376.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="31">
+        <v>5</v>
+      </c>
+      <c r="B6" s="32">
+        <v>357.9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="31">
+        <v>6</v>
+      </c>
+      <c r="B7" s="32">
+        <v>342.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="31">
+        <v>7</v>
+      </c>
+      <c r="B8" s="32">
+        <v>329.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="31">
+        <v>8</v>
+      </c>
+      <c r="B9" s="32">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="31">
+        <v>9</v>
+      </c>
+      <c r="B10" s="32">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="31">
+        <v>10</v>
+      </c>
+      <c r="B11" s="32">
+        <v>299.10000000000002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="31">
+        <v>11</v>
+      </c>
+      <c r="B12" s="32">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="31">
+        <v>12</v>
+      </c>
+      <c r="B13" s="32">
+        <v>283.60000000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="31">
+        <v>13</v>
+      </c>
+      <c r="B14" s="32">
+        <v>276.8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="31">
+        <v>14</v>
+      </c>
+      <c r="B15" s="32">
+        <v>270.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="31">
+        <v>15</v>
+      </c>
+      <c r="B16" s="32">
+        <v>264.7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="31">
+        <v>16</v>
+      </c>
+      <c r="B17" s="32">
+        <v>259.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="31">
+        <v>17</v>
+      </c>
+      <c r="B18" s="32">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="31">
+        <v>18</v>
+      </c>
+      <c r="B19" s="32">
+        <v>249.2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="31">
+        <v>19</v>
+      </c>
+      <c r="B20" s="32">
+        <v>244.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="31">
+        <v>20</v>
+      </c>
+      <c r="B21" s="32">
+        <v>240.2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="31">
+        <v>21</v>
+      </c>
+      <c r="B22" s="32">
+        <v>236.1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="31">
+        <v>22</v>
+      </c>
+      <c r="B23" s="32">
+        <v>232.1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="31">
+        <v>23</v>
+      </c>
+      <c r="B24" s="32">
+        <v>228.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="31">
+        <v>24</v>
+      </c>
+      <c r="B25" s="32">
+        <v>224.7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="31">
+        <v>25</v>
+      </c>
+      <c r="B26" s="32">
+        <v>221.3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="31">
+        <v>26</v>
+      </c>
+      <c r="B27" s="32">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="31">
+        <v>27</v>
+      </c>
+      <c r="B28" s="32">
+        <v>214.7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="31">
+        <v>28</v>
+      </c>
+      <c r="B29" s="32">
+        <v>211.7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" s="31">
+        <v>29</v>
+      </c>
+      <c r="B30" s="32">
+        <v>208.7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" s="31">
+        <v>30</v>
+      </c>
+      <c r="B31" s="32">
+        <v>205.8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="31">
+        <v>31</v>
+      </c>
+      <c r="B32" s="32">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="31">
+        <v>32</v>
+      </c>
+      <c r="B33" s="32">
+        <v>200.3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="31">
+        <v>33</v>
+      </c>
+      <c r="B34" s="32">
+        <v>175.2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="31">
+        <v>34</v>
+      </c>
+      <c r="B35" s="32">
+        <v>173.3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="31">
+        <v>35</v>
+      </c>
+      <c r="B36" s="32">
+        <v>171.4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" s="31">
+        <v>36</v>
+      </c>
+      <c r="B37" s="32">
+        <v>169.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="31">
+        <v>37</v>
+      </c>
+      <c r="B38" s="32">
+        <v>167.7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="31">
+        <v>38</v>
+      </c>
+      <c r="B39" s="32">
+        <v>165.9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="31">
+        <v>39</v>
+      </c>
+      <c r="B40" s="32">
+        <v>164.1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="31">
+        <v>40</v>
+      </c>
+      <c r="B41" s="32">
+        <v>162.4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="31">
+        <v>41</v>
+      </c>
+      <c r="B42" s="32">
+        <v>160.80000000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="31">
+        <v>42</v>
+      </c>
+      <c r="B43" s="32">
+        <v>159.1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" s="31">
+        <v>43</v>
+      </c>
+      <c r="B44" s="32">
+        <v>157.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="31">
+        <v>44</v>
+      </c>
+      <c r="B45" s="32">
+        <v>155.9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" s="31">
+        <v>45</v>
+      </c>
+      <c r="B46" s="32">
+        <v>154.30000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" s="31">
+        <v>46</v>
+      </c>
+      <c r="B47" s="32">
+        <v>152.80000000000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" s="31">
+        <v>47</v>
+      </c>
+      <c r="B48" s="32">
+        <v>151.30000000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" s="31">
+        <v>48</v>
+      </c>
+      <c r="B49" s="32">
+        <v>149.80000000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" s="31">
+        <v>49</v>
+      </c>
+      <c r="B50" s="32">
+        <v>148.4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51" s="31">
+        <v>50</v>
+      </c>
+      <c r="B51" s="32">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" s="31">
+        <v>51</v>
+      </c>
+      <c r="B52" s="32">
+        <v>145.6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" s="31">
+        <v>52</v>
+      </c>
+      <c r="B53" s="32">
+        <v>144.19999999999999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" s="31">
+        <v>53</v>
+      </c>
+      <c r="B54" s="32">
+        <v>142.80000000000001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" s="31">
+        <v>54</v>
+      </c>
+      <c r="B55" s="32">
+        <v>141.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56" s="31">
+        <v>55</v>
+      </c>
+      <c r="B56" s="32">
+        <v>140.19999999999999</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57" s="31">
+        <v>56</v>
+      </c>
+      <c r="B57" s="32">
+        <v>138.9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58" s="31">
+        <v>57</v>
+      </c>
+      <c r="B58" s="32">
+        <v>137.6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59" s="31">
+        <v>58</v>
+      </c>
+      <c r="B59" s="32">
+        <v>136.30000000000001</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A60" s="31">
+        <v>59</v>
+      </c>
+      <c r="B60" s="32">
+        <v>135.1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A61" s="31">
+        <v>60</v>
+      </c>
+      <c r="B61" s="32">
+        <v>133.9</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A62" s="31">
+        <v>61</v>
+      </c>
+      <c r="B62" s="32">
+        <v>132.69999999999999</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A63" s="31">
+        <v>62</v>
+      </c>
+      <c r="B63" s="32">
+        <v>131.4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A64" s="31">
+        <v>63</v>
+      </c>
+      <c r="B64" s="32">
+        <v>130.30000000000001</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A65" s="31">
+        <v>64</v>
+      </c>
+      <c r="B65" s="32">
+        <v>129.1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A66" s="31">
+        <v>65</v>
+      </c>
+      <c r="B66" s="32">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A67" s="31">
+        <v>66</v>
+      </c>
+      <c r="B67" s="32">
+        <v>126.9</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A68" s="31">
+        <v>67</v>
+      </c>
+      <c r="B68" s="32">
+        <v>125.8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A69" s="31">
+        <v>68</v>
+      </c>
+      <c r="B69" s="32">
+        <v>124.7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A70" s="31">
+        <v>69</v>
+      </c>
+      <c r="B70" s="32">
+        <v>123.6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A71" s="31">
+        <v>70</v>
+      </c>
+      <c r="B71" s="32">
+        <v>122.5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A72" s="31">
+        <v>71</v>
+      </c>
+      <c r="B72" s="32">
+        <v>121.5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A73" s="31">
+        <v>72</v>
+      </c>
+      <c r="B73" s="32">
+        <v>120.4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A74" s="31">
+        <v>73</v>
+      </c>
+      <c r="B74" s="32">
+        <v>119.4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A75" s="31">
+        <v>74</v>
+      </c>
+      <c r="B75" s="32">
+        <v>118.4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A76" s="31">
+        <v>75</v>
+      </c>
+      <c r="B76" s="32">
+        <v>117.4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A77" s="31">
+        <v>76</v>
+      </c>
+      <c r="B77" s="32">
+        <v>116.4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A78" s="31">
+        <v>77</v>
+      </c>
+      <c r="B78" s="32">
+        <v>115.4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A79" s="31">
+        <v>78</v>
+      </c>
+      <c r="B79" s="32">
+        <v>114.4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A80" s="31">
+        <v>79</v>
+      </c>
+      <c r="B80" s="32">
+        <v>113.5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A81" s="31">
+        <v>80</v>
+      </c>
+      <c r="B81" s="32">
+        <v>112.5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A82" s="31">
+        <v>81</v>
+      </c>
+      <c r="B82" s="32">
+        <v>111.6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A83" s="31">
+        <v>82</v>
+      </c>
+      <c r="B83" s="32">
+        <v>110.7</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A84" s="31">
+        <v>83</v>
+      </c>
+      <c r="B84" s="32">
+        <v>109.7</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A85" s="31">
+        <v>84</v>
+      </c>
+      <c r="B85" s="32">
+        <v>108.8</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A86" s="31">
+        <v>85</v>
+      </c>
+      <c r="B86" s="32">
+        <v>107.9</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A87" s="31">
+        <v>86</v>
+      </c>
+      <c r="B87" s="32">
+        <v>107.1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A88" s="31">
+        <v>87</v>
+      </c>
+      <c r="B88" s="32">
+        <v>106.2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A89" s="31">
+        <v>88</v>
+      </c>
+      <c r="B89" s="32">
+        <v>105.3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A90" s="31">
+        <v>89</v>
+      </c>
+      <c r="B90" s="32">
+        <v>104.4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A91" s="31">
+        <v>90</v>
+      </c>
+      <c r="B91" s="32">
+        <v>103.6</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A92" s="31">
+        <v>91</v>
+      </c>
+      <c r="B92" s="32">
+        <v>102.7</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A93" s="31">
+        <v>92</v>
+      </c>
+      <c r="B93" s="32">
+        <v>101.9</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A94" s="31">
+        <v>93</v>
+      </c>
+      <c r="B94" s="32">
+        <v>101.1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A95" s="31">
+        <v>94</v>
+      </c>
+      <c r="B95" s="32">
+        <v>100.3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A96" s="31">
+        <v>95</v>
+      </c>
+      <c r="B96" s="32">
+        <v>99.4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A97" s="31">
+        <v>96</v>
+      </c>
+      <c r="B97" s="32">
+        <v>98.6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A98" s="31">
+        <v>97</v>
+      </c>
+      <c r="B98" s="32">
+        <v>97.8</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A99" s="31">
+        <v>98</v>
+      </c>
+      <c r="B99" s="32">
+        <v>97.1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A100" s="31">
+        <v>99</v>
+      </c>
+      <c r="B100" s="32">
+        <v>96.3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A101" s="31">
+        <v>100</v>
+      </c>
+      <c r="B101" s="32">
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A102" s="31">
+        <v>101</v>
+      </c>
+      <c r="B102" s="32">
+        <v>94.7</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A103" s="31">
+        <v>102</v>
+      </c>
+      <c r="B103" s="32">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A104" s="31">
+        <v>103</v>
+      </c>
+      <c r="B104" s="32">
+        <v>93.2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A105" s="31">
+        <v>104</v>
+      </c>
+      <c r="B105" s="32">
+        <v>92.5</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A106" s="31">
+        <v>105</v>
+      </c>
+      <c r="B106" s="32">
+        <v>91.7</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A107" s="31">
+        <v>106</v>
+      </c>
+      <c r="B107" s="32">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A108" s="31">
+        <v>107</v>
+      </c>
+      <c r="B108" s="32">
+        <v>90.3</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A109" s="31">
+        <v>108</v>
+      </c>
+      <c r="B109" s="32">
+        <v>89.5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A110" s="31">
+        <v>109</v>
+      </c>
+      <c r="B110" s="32">
+        <v>88.8</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A111" s="31">
+        <v>110</v>
+      </c>
+      <c r="B111" s="32">
+        <v>88.1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A112" s="31">
+        <v>111</v>
+      </c>
+      <c r="B112" s="32">
+        <v>87.4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A113" s="31">
+        <v>112</v>
+      </c>
+      <c r="B113" s="32">
+        <v>86.7</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A114" s="31">
+        <v>113</v>
+      </c>
+      <c r="B114" s="32">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A115" s="31">
+        <v>114</v>
+      </c>
+      <c r="B115" s="32">
+        <v>85.3</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A116" s="31">
+        <v>115</v>
+      </c>
+      <c r="B116" s="32">
+        <v>84.6</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A117" s="31">
+        <v>116</v>
+      </c>
+      <c r="B117" s="32">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A118" s="31">
+        <v>117</v>
+      </c>
+      <c r="B118" s="32">
+        <v>83.3</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A119" s="31">
+        <v>118</v>
+      </c>
+      <c r="B119" s="32">
+        <v>82.6</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A120" s="31">
+        <v>119</v>
+      </c>
+      <c r="B120" s="32">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A121" s="31">
+        <v>120</v>
+      </c>
+      <c r="B121" s="32">
+        <v>81.3</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A122" s="31">
+        <v>121</v>
+      </c>
+      <c r="B122" s="32">
+        <v>80.7</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A123" s="31">
+        <v>122</v>
+      </c>
+      <c r="B123" s="32">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A124" s="31">
+        <v>123</v>
+      </c>
+      <c r="B124" s="32">
+        <v>79.400000000000006</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A125" s="31">
+        <v>124</v>
+      </c>
+      <c r="B125" s="32">
+        <v>78.7</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A126" s="31">
+        <v>125</v>
+      </c>
+      <c r="B126" s="32">
+        <v>78.099999999999994</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A127" s="31">
+        <v>126</v>
+      </c>
+      <c r="B127" s="32">
+        <v>77.5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A128" s="31">
+        <v>127</v>
+      </c>
+      <c r="B128" s="32">
+        <v>76.900000000000006</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A129" s="31">
+        <v>128</v>
+      </c>
+      <c r="B129" s="32">
+        <v>76.2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A130" s="31">
+        <v>129</v>
+      </c>
+      <c r="B130" s="32">
+        <v>75.599999999999994</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A131" s="31">
+        <v>130</v>
+      </c>
+      <c r="B131" s="32">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A132" s="31">
+        <v>131</v>
+      </c>
+      <c r="B132" s="32">
+        <v>74.400000000000006</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A133" s="31">
+        <v>132</v>
+      </c>
+      <c r="B133" s="32">
+        <v>73.8</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A134" s="31">
+        <v>133</v>
+      </c>
+      <c r="B134" s="32">
+        <v>73.2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A135" s="31">
+        <v>134</v>
+      </c>
+      <c r="B135" s="32">
+        <v>72.599999999999994</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A136" s="31">
+        <v>135</v>
+      </c>
+      <c r="B136" s="32">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A137" s="31">
+        <v>136</v>
+      </c>
+      <c r="B137" s="32">
+        <v>71.5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A138" s="31">
+        <v>137</v>
+      </c>
+      <c r="B138" s="32">
+        <v>70.900000000000006</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A139" s="31">
+        <v>138</v>
+      </c>
+      <c r="B139" s="32">
+        <v>70.3</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A140" s="31">
+        <v>139</v>
+      </c>
+      <c r="B140" s="32">
+        <v>69.7</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A141" s="31">
+        <v>140</v>
+      </c>
+      <c r="B141" s="32">
+        <v>69.2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A142" s="31">
+        <v>141</v>
+      </c>
+      <c r="B142" s="32">
+        <v>68.599999999999994</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A143" s="31">
+        <v>142</v>
+      </c>
+      <c r="B143" s="32">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A144" s="31">
+        <v>143</v>
+      </c>
+      <c r="B144" s="32">
+        <v>67.5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A145" s="31">
+        <v>144</v>
+      </c>
+      <c r="B145" s="32">
+        <v>66.900000000000006</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A146" s="31">
+        <v>145</v>
+      </c>
+      <c r="B146" s="32">
+        <v>66.400000000000006</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A147" s="31">
+        <v>146</v>
+      </c>
+      <c r="B147" s="32">
+        <v>65.8</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A148" s="31">
+        <v>147</v>
+      </c>
+      <c r="B148" s="32">
+        <v>65.3</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A149" s="31">
+        <v>148</v>
+      </c>
+      <c r="B149" s="32">
+        <v>64.8</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A150" s="31">
+        <v>149</v>
+      </c>
+      <c r="B150" s="32">
+        <v>64.2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A151" s="31">
+        <v>150</v>
+      </c>
+      <c r="B151" s="32">
+        <v>63.7</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A152" s="31">
+        <v>151</v>
+      </c>
+      <c r="B152" s="32">
+        <v>63.2</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A153" s="31">
+        <v>152</v>
+      </c>
+      <c r="B153" s="32">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A154" s="31">
+        <v>153</v>
+      </c>
+      <c r="B154" s="32">
+        <v>62.1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A155" s="31">
+        <v>154</v>
+      </c>
+      <c r="B155" s="32">
+        <v>61.6</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A156" s="31">
+        <v>155</v>
+      </c>
+      <c r="B156" s="32">
+        <v>61.1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A157" s="31">
+        <v>156</v>
+      </c>
+      <c r="B157" s="32">
+        <v>60.6</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A158" s="31">
+        <v>157</v>
+      </c>
+      <c r="B158" s="32">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A159" s="31">
+        <v>158</v>
+      </c>
+      <c r="B159" s="32">
+        <v>59.5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A160" s="31">
+        <v>159</v>
+      </c>
+      <c r="B160" s="32">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A161" s="31">
+        <v>160</v>
+      </c>
+      <c r="B161" s="32">
+        <v>58.5</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A162" s="31">
+        <v>161</v>
+      </c>
+      <c r="B162" s="32">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A163" s="31">
+        <v>162</v>
+      </c>
+      <c r="B163" s="32">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A164" s="31">
+        <v>163</v>
+      </c>
+      <c r="B164" s="32">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A165" s="31">
+        <v>164</v>
+      </c>
+      <c r="B165" s="32">
+        <v>56.6</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A166" s="31">
+        <v>165</v>
+      </c>
+      <c r="B166" s="32">
+        <v>56.1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A167" s="31">
+        <v>166</v>
+      </c>
+      <c r="B167" s="32">
+        <v>55.6</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A168" s="31">
+        <v>167</v>
+      </c>
+      <c r="B168" s="32">
+        <v>55.1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A169" s="31">
+        <v>168</v>
+      </c>
+      <c r="B169" s="32">
+        <v>54.6</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A170" s="31">
+        <v>169</v>
+      </c>
+      <c r="B170" s="32">
+        <v>54.2</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A171" s="31">
+        <v>170</v>
+      </c>
+      <c r="B171" s="32">
+        <v>53.7</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A172" s="31">
+        <v>171</v>
+      </c>
+      <c r="B172" s="32">
+        <v>53.2</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A173" s="31">
+        <v>172</v>
+      </c>
+      <c r="B173" s="32">
+        <v>52.7</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A174" s="31">
+        <v>173</v>
+      </c>
+      <c r="B174" s="32">
+        <v>52.3</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A175" s="31">
+        <v>174</v>
+      </c>
+      <c r="B175" s="32">
+        <v>51.8</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A176" s="31">
+        <v>175</v>
+      </c>
+      <c r="B176" s="32">
+        <v>51.4</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A177" s="31">
+        <v>176</v>
+      </c>
+      <c r="B177" s="32">
+        <v>50.9</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A178" s="31">
+        <v>177</v>
+      </c>
+      <c r="B178" s="32">
+        <v>50.4</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A179" s="31">
+        <v>178</v>
+      </c>
+      <c r="B179" s="32">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A180" s="31">
+        <v>179</v>
+      </c>
+      <c r="B180" s="32">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A181" s="31">
+        <v>180</v>
+      </c>
+      <c r="B181" s="32">
+        <v>49.1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A182" s="31">
+        <v>181</v>
+      </c>
+      <c r="B182" s="32">
+        <v>48.6</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A183" s="31">
+        <v>182</v>
+      </c>
+      <c r="B183" s="32">
+        <v>48.2</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A184" s="31">
+        <v>183</v>
+      </c>
+      <c r="B184" s="32">
+        <v>47.8</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A185" s="31">
+        <v>184</v>
+      </c>
+      <c r="B185" s="32">
+        <v>47.3</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A186" s="31">
+        <v>185</v>
+      </c>
+      <c r="B186" s="32">
+        <v>46.9</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A187" s="31">
+        <v>186</v>
+      </c>
+      <c r="B187" s="32">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A188" s="31">
+        <v>187</v>
+      </c>
+      <c r="B188" s="32">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A189" s="31">
+        <v>188</v>
+      </c>
+      <c r="B189" s="32">
+        <v>45.6</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A190" s="31">
+        <v>189</v>
+      </c>
+      <c r="B190" s="32">
+        <v>45.2</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A191" s="31">
+        <v>190</v>
+      </c>
+      <c r="B191" s="32">
+        <v>44.7</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A192" s="31">
+        <v>191</v>
+      </c>
+      <c r="B192" s="32">
+        <v>44.3</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A193" s="31">
+        <v>192</v>
+      </c>
+      <c r="B193" s="32">
+        <v>43.9</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A194" s="31">
+        <v>193</v>
+      </c>
+      <c r="B194" s="32">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A195" s="31">
+        <v>194</v>
+      </c>
+      <c r="B195" s="32">
+        <v>43.1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A196" s="31">
+        <v>195</v>
+      </c>
+      <c r="B196" s="32">
+        <v>42.6</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A197" s="31">
+        <v>196</v>
+      </c>
+      <c r="B197" s="32">
+        <v>42.2</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A198" s="31">
+        <v>197</v>
+      </c>
+      <c r="B198" s="32">
+        <v>41.8</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A199" s="31">
+        <v>198</v>
+      </c>
+      <c r="B199" s="32">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A200" s="31">
+        <v>199</v>
+      </c>
+      <c r="B200" s="32">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A201" s="31">
+        <v>200</v>
+      </c>
+      <c r="B201" s="32">
+        <v>40.6</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A202" s="31">
+        <v>201</v>
+      </c>
+      <c r="B202" s="32">
+        <v>40.200000000000003</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A203" s="31">
+        <v>202</v>
+      </c>
+      <c r="B203" s="32">
+        <v>39.799999999999997</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A204" s="31">
+        <v>203</v>
+      </c>
+      <c r="B204" s="32">
+        <v>39.4</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A205" s="31">
+        <v>204</v>
+      </c>
+      <c r="B205" s="32">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A206" s="31">
+        <v>205</v>
+      </c>
+      <c r="B206" s="32">
+        <v>38.6</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A207" s="31">
+        <v>206</v>
+      </c>
+      <c r="B207" s="32">
+        <v>38.200000000000003</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A208" s="31">
+        <v>207</v>
+      </c>
+      <c r="B208" s="32">
+        <v>37.799999999999997</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A209" s="31">
+        <v>208</v>
+      </c>
+      <c r="B209" s="32">
+        <v>37.4</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A210" s="31">
+        <v>209</v>
+      </c>
+      <c r="B210" s="32">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A211" s="31">
+        <v>210</v>
+      </c>
+      <c r="B211" s="32">
+        <v>36.6</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A212" s="31">
+        <v>211</v>
+      </c>
+      <c r="B212" s="32">
+        <v>36.299999999999997</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A213" s="31">
+        <v>212</v>
+      </c>
+      <c r="B213" s="32">
+        <v>35.9</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A214" s="31">
+        <v>213</v>
+      </c>
+      <c r="B214" s="32">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A215" s="31">
+        <v>214</v>
+      </c>
+      <c r="B215" s="32">
+        <v>35.1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A216" s="31">
+        <v>215</v>
+      </c>
+      <c r="B216" s="32">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A217" s="31">
+        <v>216</v>
+      </c>
+      <c r="B217" s="32">
+        <v>43.1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A218" s="31">
+        <v>217</v>
+      </c>
+      <c r="B218" s="32">
+        <v>42.6</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A219" s="31">
+        <v>218</v>
+      </c>
+      <c r="B219" s="32">
+        <v>42.2</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A220" s="31">
+        <v>219</v>
+      </c>
+      <c r="B220" s="32">
+        <v>41.8</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A221" s="31">
+        <v>220</v>
+      </c>
+      <c r="B221" s="32">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A222" s="31">
+        <v>221</v>
+      </c>
+      <c r="B222" s="32">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A223" s="31">
+        <v>222</v>
+      </c>
+      <c r="B223" s="32">
+        <v>40.6</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A224" s="31">
+        <v>223</v>
+      </c>
+      <c r="B224" s="32">
+        <v>40.200000000000003</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A225" s="31">
+        <v>224</v>
+      </c>
+      <c r="B225" s="32">
+        <v>39.799999999999997</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A226" s="31">
+        <v>225</v>
+      </c>
+      <c r="B226" s="32">
+        <v>39.4</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A227" s="31">
+        <v>226</v>
+      </c>
+      <c r="B227" s="32">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A228" s="31">
+        <v>227</v>
+      </c>
+      <c r="B228" s="32">
+        <v>38.6</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A229" s="31">
+        <v>228</v>
+      </c>
+      <c r="B229" s="32">
+        <v>38.200000000000003</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A230" s="31">
+        <v>229</v>
+      </c>
+      <c r="B230" s="32">
+        <v>37.799999999999997</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A231" s="31">
+        <v>230</v>
+      </c>
+      <c r="B231" s="32">
+        <v>37.4</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A232" s="31">
+        <v>231</v>
+      </c>
+      <c r="B232" s="32">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A233" s="31">
+        <v>232</v>
+      </c>
+      <c r="B233" s="32">
+        <v>36.6</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A234" s="31">
+        <v>233</v>
+      </c>
+      <c r="B234" s="32">
+        <v>36.200000000000003</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A235" s="31">
+        <v>234</v>
+      </c>
+      <c r="B235" s="32">
+        <v>35.799999999999997</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A236" s="31">
+        <v>235</v>
+      </c>
+      <c r="B236" s="32">
+        <v>35.4</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A237" s="31">
+        <v>236</v>
+      </c>
+      <c r="B237" s="32">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A238" s="31">
+        <v>237</v>
+      </c>
+      <c r="B238" s="32">
+        <v>34.6</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A239" s="31">
+        <v>238</v>
+      </c>
+      <c r="B239" s="32">
+        <v>34.200000000000003</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A240" s="31">
+        <v>239</v>
+      </c>
+      <c r="B240" s="32">
+        <v>33.799999999999997</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A241" s="31">
+        <v>240</v>
+      </c>
+      <c r="B241" s="32">
+        <v>33.4</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A242" s="31">
+        <v>241</v>
+      </c>
+      <c r="B242" s="32">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A243" s="31">
+        <v>242</v>
+      </c>
+      <c r="B243" s="32">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A244" s="31">
+        <v>243</v>
+      </c>
+      <c r="B244" s="32">
+        <v>32.200000000000003</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A245" s="31">
+        <v>244</v>
+      </c>
+      <c r="B245" s="32">
+        <v>31.8</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A246" s="31">
+        <v>245</v>
+      </c>
+      <c r="B246" s="32">
+        <v>31.4</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A247" s="31">
+        <v>246</v>
+      </c>
+      <c r="B247" s="32">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A248" s="31">
+        <v>247</v>
+      </c>
+      <c r="B248" s="32">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A249" s="31">
+        <v>248</v>
+      </c>
+      <c r="B249" s="32">
+        <v>30.2</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A250" s="31">
+        <v>249</v>
+      </c>
+      <c r="B250" s="32">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A251" s="31">
+        <v>250</v>
+      </c>
+      <c r="B251" s="32">
+        <v>29.4</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A252" s="31">
+        <v>251</v>
+      </c>
+      <c r="B252" s="32">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A253" s="31">
+        <v>252</v>
+      </c>
+      <c r="B253" s="32">
+        <v>28.6</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A254" s="31">
+        <v>253</v>
+      </c>
+      <c r="B254" s="32">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A255" s="31">
+        <v>254</v>
+      </c>
+      <c r="B255" s="32">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A256" s="31">
+        <v>255</v>
+      </c>
+      <c r="B256" s="32">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A257" s="31">
+        <v>256</v>
+      </c>
+      <c r="B257" s="32">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A258" s="31">
+        <v>257</v>
+      </c>
+      <c r="B258" s="32">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A259" s="31">
+        <v>258</v>
+      </c>
+      <c r="B259" s="32">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A260" s="31">
+        <v>259</v>
+      </c>
+      <c r="B260" s="32">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A261" s="31">
+        <v>260</v>
+      </c>
+      <c r="B261" s="32">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A262" s="31">
+        <v>261</v>
+      </c>
+      <c r="B262" s="32">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A263" s="31">
+        <v>262</v>
+      </c>
+      <c r="B263" s="32">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A264" s="31">
+        <v>263</v>
+      </c>
+      <c r="B264" s="32">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A265" s="31">
+        <v>264</v>
+      </c>
+      <c r="B265" s="32">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A266" s="31">
+        <v>265</v>
+      </c>
+      <c r="B266" s="32">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A267" s="31">
+        <v>266</v>
+      </c>
+      <c r="B267" s="32">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A268" s="31">
+        <v>267</v>
+      </c>
+      <c r="B268" s="32">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A269" s="31">
+        <v>268</v>
+      </c>
+      <c r="B269" s="32">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A270" s="31">
+        <v>269</v>
+      </c>
+      <c r="B270" s="32">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A271" s="31">
+        <v>270</v>
+      </c>
+      <c r="B271" s="32">
+        <v>21.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBFC2E4E-DE67-CC43-9BD5-21851DBEFD53}">
+  <dimension ref="A1:B271"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="30" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="31">
+        <v>1</v>
+      </c>
+      <c r="B2" s="32">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="31">
+        <v>2</v>
+      </c>
+      <c r="B3" s="32">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="31">
+        <v>3</v>
+      </c>
+      <c r="B4" s="32">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="31">
+        <v>4</v>
+      </c>
+      <c r="B5" s="32">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="31">
+        <v>5</v>
+      </c>
+      <c r="B6" s="32">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="31">
+        <v>6</v>
+      </c>
+      <c r="B7" s="32">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="31">
+        <v>7</v>
+      </c>
+      <c r="B8" s="32">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="31">
+        <v>8</v>
+      </c>
+      <c r="B9" s="32">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="31">
+        <v>9</v>
+      </c>
+      <c r="B10" s="32">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="31">
+        <v>10</v>
+      </c>
+      <c r="B11" s="32">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="31">
+        <v>11</v>
+      </c>
+      <c r="B12" s="32">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="31">
+        <v>12</v>
+      </c>
+      <c r="B13" s="32">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="31">
+        <v>13</v>
+      </c>
+      <c r="B14" s="32">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="31">
+        <v>14</v>
+      </c>
+      <c r="B15" s="32">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="31">
+        <v>15</v>
+      </c>
+      <c r="B16" s="32">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="31">
+        <v>16</v>
+      </c>
+      <c r="B17" s="32">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="31">
+        <v>17</v>
+      </c>
+      <c r="B18" s="32">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="31">
+        <v>18</v>
+      </c>
+      <c r="B19" s="32">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="31">
+        <v>19</v>
+      </c>
+      <c r="B20" s="32">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="31">
+        <v>20</v>
+      </c>
+      <c r="B21" s="32">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="31">
+        <v>21</v>
+      </c>
+      <c r="B22" s="32">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="31">
+        <v>22</v>
+      </c>
+      <c r="B23" s="32">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="31">
+        <v>23</v>
+      </c>
+      <c r="B24" s="32">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="31">
+        <v>24</v>
+      </c>
+      <c r="B25" s="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="31">
+        <v>25</v>
+      </c>
+      <c r="B26" s="32">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="31">
+        <v>26</v>
+      </c>
+      <c r="B27" s="32">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="31">
+        <v>27</v>
+      </c>
+      <c r="B28" s="32">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="31">
+        <v>28</v>
+      </c>
+      <c r="B29" s="32">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" s="31">
+        <v>29</v>
+      </c>
+      <c r="B30" s="32">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" s="31">
+        <v>30</v>
+      </c>
+      <c r="B31" s="32">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="31">
+        <v>31</v>
+      </c>
+      <c r="B32" s="32">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="31">
+        <v>32</v>
+      </c>
+      <c r="B33" s="32">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="31">
+        <v>33</v>
+      </c>
+      <c r="B34" s="32">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="31">
+        <v>34</v>
+      </c>
+      <c r="B35" s="32">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="31">
+        <v>35</v>
+      </c>
+      <c r="B36" s="32">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" s="31">
+        <v>36</v>
+      </c>
+      <c r="B37" s="32">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="31">
+        <v>37</v>
+      </c>
+      <c r="B38" s="32">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="31">
+        <v>38</v>
+      </c>
+      <c r="B39" s="32">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="31">
+        <v>39</v>
+      </c>
+      <c r="B40" s="32">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="31">
+        <v>40</v>
+      </c>
+      <c r="B41" s="32">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="31">
+        <v>41</v>
+      </c>
+      <c r="B42" s="32">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="31">
+        <v>42</v>
+      </c>
+      <c r="B43" s="32">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" s="31">
+        <v>43</v>
+      </c>
+      <c r="B44" s="32">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="31">
+        <v>44</v>
+      </c>
+      <c r="B45" s="32">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" s="31">
+        <v>45</v>
+      </c>
+      <c r="B46" s="32">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" s="31">
+        <v>46</v>
+      </c>
+      <c r="B47" s="32">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" s="31">
+        <v>47</v>
+      </c>
+      <c r="B48" s="32">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" s="31">
+        <v>48</v>
+      </c>
+      <c r="B49" s="32">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" s="31">
+        <v>49</v>
+      </c>
+      <c r="B50" s="32">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51" s="31">
+        <v>50</v>
+      </c>
+      <c r="B51" s="32">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" s="31">
+        <v>51</v>
+      </c>
+      <c r="B52" s="32">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" s="31">
+        <v>52</v>
+      </c>
+      <c r="B53" s="32">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" s="31">
+        <v>53</v>
+      </c>
+      <c r="B54" s="32">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" s="31">
+        <v>54</v>
+      </c>
+      <c r="B55" s="32">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56" s="31">
+        <v>55</v>
+      </c>
+      <c r="B56" s="32">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57" s="31">
+        <v>56</v>
+      </c>
+      <c r="B57" s="32">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58" s="31">
+        <v>57</v>
+      </c>
+      <c r="B58" s="32">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59" s="31">
+        <v>58</v>
+      </c>
+      <c r="B59" s="32">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A60" s="31">
+        <v>59</v>
+      </c>
+      <c r="B60" s="32">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A61" s="31">
+        <v>60</v>
+      </c>
+      <c r="B61" s="32">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A62" s="31">
+        <v>61</v>
+      </c>
+      <c r="B62" s="32">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A63" s="31">
+        <v>62</v>
+      </c>
+      <c r="B63" s="32">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A64" s="31">
+        <v>63</v>
+      </c>
+      <c r="B64" s="32">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A65" s="31">
+        <v>64</v>
+      </c>
+      <c r="B65" s="32">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A66" s="31">
+        <v>65</v>
+      </c>
+      <c r="B66" s="32">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A67" s="31">
+        <v>66</v>
+      </c>
+      <c r="B67" s="32">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A68" s="31">
+        <v>67</v>
+      </c>
+      <c r="B68" s="32">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A69" s="31">
+        <v>68</v>
+      </c>
+      <c r="B69" s="32">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A70" s="31">
+        <v>69</v>
+      </c>
+      <c r="B70" s="32">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A71" s="31">
+        <v>70</v>
+      </c>
+      <c r="B71" s="32">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A72" s="31">
+        <v>71</v>
+      </c>
+      <c r="B72" s="32">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A73" s="31">
+        <v>72</v>
+      </c>
+      <c r="B73" s="32">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A74" s="31">
+        <v>73</v>
+      </c>
+      <c r="B74" s="32">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A75" s="31">
+        <v>74</v>
+      </c>
+      <c r="B75" s="32">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A76" s="31">
+        <v>75</v>
+      </c>
+      <c r="B76" s="32">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A77" s="31">
+        <v>76</v>
+      </c>
+      <c r="B77" s="32">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A78" s="31">
+        <v>77</v>
+      </c>
+      <c r="B78" s="32">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A79" s="31">
+        <v>78</v>
+      </c>
+      <c r="B79" s="32">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A80" s="31">
+        <v>79</v>
+      </c>
+      <c r="B80" s="32">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A81" s="31">
+        <v>80</v>
+      </c>
+      <c r="B81" s="32">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A82" s="31">
+        <v>81</v>
+      </c>
+      <c r="B82" s="32">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A83" s="31">
+        <v>82</v>
+      </c>
+      <c r="B83" s="32">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A84" s="31">
+        <v>83</v>
+      </c>
+      <c r="B84" s="32">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A85" s="31">
+        <v>84</v>
+      </c>
+      <c r="B85" s="32">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A86" s="31">
+        <v>85</v>
+      </c>
+      <c r="B86" s="32">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A87" s="31">
+        <v>86</v>
+      </c>
+      <c r="B87" s="32">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A88" s="31">
+        <v>87</v>
+      </c>
+      <c r="B88" s="32">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A89" s="31">
+        <v>88</v>
+      </c>
+      <c r="B89" s="32">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A90" s="31">
+        <v>89</v>
+      </c>
+      <c r="B90" s="32">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A91" s="31">
+        <v>90</v>
+      </c>
+      <c r="B91" s="32">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A92" s="31">
+        <v>91</v>
+      </c>
+      <c r="B92" s="32">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A93" s="31">
+        <v>92</v>
+      </c>
+      <c r="B93" s="32">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A94" s="31">
+        <v>93</v>
+      </c>
+      <c r="B94" s="32">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A95" s="31">
+        <v>94</v>
+      </c>
+      <c r="B95" s="32">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A96" s="31">
+        <v>95</v>
+      </c>
+      <c r="B96" s="32">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A97" s="31">
+        <v>96</v>
+      </c>
+      <c r="B97" s="32">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A98" s="31">
+        <v>97</v>
+      </c>
+      <c r="B98" s="32">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A99" s="31">
+        <v>98</v>
+      </c>
+      <c r="B99" s="32">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A100" s="31">
+        <v>99</v>
+      </c>
+      <c r="B100" s="32">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A101" s="31">
+        <v>100</v>
+      </c>
+      <c r="B101" s="32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A102" s="31">
+        <v>101</v>
+      </c>
+      <c r="B102" s="32">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A103" s="31">
+        <v>102</v>
+      </c>
+      <c r="B103" s="32">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A104" s="31">
+        <v>103</v>
+      </c>
+      <c r="B104" s="32">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A105" s="31">
+        <v>104</v>
+      </c>
+      <c r="B105" s="32">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A106" s="31">
+        <v>105</v>
+      </c>
+      <c r="B106" s="32">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A107" s="31">
+        <v>106</v>
+      </c>
+      <c r="B107" s="32">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A108" s="31">
+        <v>107</v>
+      </c>
+      <c r="B108" s="32">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A109" s="31">
+        <v>108</v>
+      </c>
+      <c r="B109" s="32">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A110" s="31">
+        <v>109</v>
+      </c>
+      <c r="B110" s="32">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A111" s="31">
+        <v>110</v>
+      </c>
+      <c r="B111" s="32">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A112" s="31">
+        <v>111</v>
+      </c>
+      <c r="B112" s="32">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A113" s="31">
+        <v>112</v>
+      </c>
+      <c r="B113" s="32">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A114" s="31">
+        <v>113</v>
+      </c>
+      <c r="B114" s="32">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A115" s="31">
+        <v>114</v>
+      </c>
+      <c r="B115" s="32">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A116" s="31">
+        <v>115</v>
+      </c>
+      <c r="B116" s="32">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A117" s="31">
+        <v>116</v>
+      </c>
+      <c r="B117" s="32">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A118" s="31">
+        <v>117</v>
+      </c>
+      <c r="B118" s="32">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A119" s="31">
+        <v>118</v>
+      </c>
+      <c r="B119" s="32">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A120" s="31">
+        <v>119</v>
+      </c>
+      <c r="B120" s="32">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A121" s="31">
+        <v>120</v>
+      </c>
+      <c r="B121" s="32">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A122" s="31">
+        <v>121</v>
+      </c>
+      <c r="B122" s="32">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A123" s="31">
+        <v>122</v>
+      </c>
+      <c r="B123" s="32">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A124" s="31">
+        <v>123</v>
+      </c>
+      <c r="B124" s="32">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A125" s="31">
+        <v>124</v>
+      </c>
+      <c r="B125" s="32">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A126" s="31">
+        <v>125</v>
+      </c>
+      <c r="B126" s="32">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A127" s="31">
+        <v>126</v>
+      </c>
+      <c r="B127" s="32">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A128" s="31">
+        <v>127</v>
+      </c>
+      <c r="B128" s="32">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A129" s="31">
+        <v>128</v>
+      </c>
+      <c r="B129" s="32">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A130" s="31">
+        <v>129</v>
+      </c>
+      <c r="B130" s="32">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A131" s="31">
+        <v>130</v>
+      </c>
+      <c r="B131" s="32">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A132" s="31">
+        <v>131</v>
+      </c>
+      <c r="B132" s="32">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A133" s="31">
+        <v>132</v>
+      </c>
+      <c r="B133" s="32">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A134" s="31">
+        <v>133</v>
+      </c>
+      <c r="B134" s="32">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A135" s="31">
+        <v>134</v>
+      </c>
+      <c r="B135" s="32">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A136" s="31">
+        <v>135</v>
+      </c>
+      <c r="B136" s="32">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A137" s="31">
+        <v>136</v>
+      </c>
+      <c r="B137" s="32">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A138" s="31">
+        <v>137</v>
+      </c>
+      <c r="B138" s="32">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A139" s="31">
+        <v>138</v>
+      </c>
+      <c r="B139" s="32">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A140" s="31">
+        <v>139</v>
+      </c>
+      <c r="B140" s="32">
+        <v>36.5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A141" s="31">
+        <v>140</v>
+      </c>
+      <c r="B141" s="32">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A142" s="31">
+        <v>141</v>
+      </c>
+      <c r="B142" s="32">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A143" s="31">
+        <v>142</v>
+      </c>
+      <c r="B143" s="32">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A144" s="31">
+        <v>143</v>
+      </c>
+      <c r="B144" s="32">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A145" s="31">
+        <v>144</v>
+      </c>
+      <c r="B145" s="32">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A146" s="31">
+        <v>145</v>
+      </c>
+      <c r="B146" s="32">
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A147" s="31">
+        <v>146</v>
+      </c>
+      <c r="B147" s="32">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A148" s="31">
+        <v>147</v>
+      </c>
+      <c r="B148" s="32">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A149" s="31">
+        <v>148</v>
+      </c>
+      <c r="B149" s="32">
+        <v>32.200000000000003</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A150" s="31">
+        <v>149</v>
+      </c>
+      <c r="B150" s="32">
+        <v>31.8</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A151" s="31">
+        <v>150</v>
+      </c>
+      <c r="B151" s="32">
+        <v>31.4</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A152" s="31">
+        <v>151</v>
+      </c>
+      <c r="B152" s="32">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A153" s="31">
+        <v>152</v>
+      </c>
+      <c r="B153" s="32">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A154" s="31">
+        <v>153</v>
+      </c>
+      <c r="B154" s="32">
+        <v>30.2</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A155" s="31">
+        <v>154</v>
+      </c>
+      <c r="B155" s="32">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A156" s="31">
+        <v>155</v>
+      </c>
+      <c r="B156" s="32">
+        <v>29.4</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A157" s="31">
+        <v>156</v>
+      </c>
+      <c r="B157" s="32">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A158" s="31">
+        <v>157</v>
+      </c>
+      <c r="B158" s="32">
+        <v>28.6</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A159" s="31">
+        <v>158</v>
+      </c>
+      <c r="B159" s="32">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A160" s="31">
+        <v>159</v>
+      </c>
+      <c r="B160" s="32">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A161" s="31">
+        <v>160</v>
+      </c>
+      <c r="B161" s="32">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A162" s="31">
+        <v>161</v>
+      </c>
+      <c r="B162" s="32">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A163" s="31">
+        <v>162</v>
+      </c>
+      <c r="B163" s="32">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A164" s="31">
+        <v>163</v>
+      </c>
+      <c r="B164" s="32">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A165" s="31">
+        <v>164</v>
+      </c>
+      <c r="B165" s="32">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A166" s="31">
+        <v>165</v>
+      </c>
+      <c r="B166" s="32">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A167" s="31">
+        <v>166</v>
+      </c>
+      <c r="B167" s="32">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A168" s="31">
+        <v>167</v>
+      </c>
+      <c r="B168" s="32">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A169" s="31">
+        <v>168</v>
+      </c>
+      <c r="B169" s="32">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A170" s="31">
+        <v>169</v>
+      </c>
+      <c r="B170" s="32">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A171" s="31">
+        <v>170</v>
+      </c>
+      <c r="B171" s="32">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A172" s="31">
+        <v>171</v>
+      </c>
+      <c r="B172" s="32">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A173" s="31">
+        <v>172</v>
+      </c>
+      <c r="B173" s="32">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A174" s="31">
+        <v>173</v>
+      </c>
+      <c r="B174" s="32">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A175" s="31">
+        <v>174</v>
+      </c>
+      <c r="B175" s="32">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A176" s="31">
+        <v>175</v>
+      </c>
+      <c r="B176" s="32">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A177" s="31">
+        <v>176</v>
+      </c>
+      <c r="B177" s="32">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A178" s="31">
+        <v>177</v>
+      </c>
+      <c r="B178" s="32">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A179" s="31">
+        <v>178</v>
+      </c>
+      <c r="B179" s="32">
+        <v>20.2</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A180" s="31">
+        <v>179</v>
+      </c>
+      <c r="B180" s="32">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A181" s="31">
+        <v>180</v>
+      </c>
+      <c r="B181" s="32">
+        <v>19.399999999999999</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A182" s="31">
+        <v>181</v>
+      </c>
+      <c r="B182" s="32">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A183" s="31">
+        <v>182</v>
+      </c>
+      <c r="B183" s="32">
+        <v>18.600000000000001</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A184" s="31">
+        <v>183</v>
+      </c>
+      <c r="B184" s="32">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A185" s="31">
+        <v>184</v>
+      </c>
+      <c r="B185" s="32">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A186" s="31">
+        <v>185</v>
+      </c>
+      <c r="B186" s="32">
+        <v>17.399999999999999</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A187" s="31">
+        <v>186</v>
+      </c>
+      <c r="B187" s="32">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A188" s="31">
+        <v>187</v>
+      </c>
+      <c r="B188" s="32">
+        <v>16.600000000000001</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A189" s="31">
+        <v>188</v>
+      </c>
+      <c r="B189" s="32">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A190" s="31">
+        <v>189</v>
+      </c>
+      <c r="B190" s="32">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A191" s="31">
+        <v>190</v>
+      </c>
+      <c r="B191" s="32">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A192" s="31">
+        <v>191</v>
+      </c>
+      <c r="B192" s="32">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A193" s="31">
+        <v>192</v>
+      </c>
+      <c r="B193" s="32">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A194" s="31">
+        <v>193</v>
+      </c>
+      <c r="B194" s="32">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A195" s="31">
+        <v>194</v>
+      </c>
+      <c r="B195" s="32">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A196" s="31">
+        <v>195</v>
+      </c>
+      <c r="B196" s="32">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A197" s="31">
+        <v>196</v>
+      </c>
+      <c r="B197" s="32">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A198" s="31">
+        <v>197</v>
+      </c>
+      <c r="B198" s="32">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A199" s="31">
+        <v>198</v>
+      </c>
+      <c r="B199" s="32">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A200" s="31">
+        <v>199</v>
+      </c>
+      <c r="B200" s="32">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A201" s="31">
+        <v>200</v>
+      </c>
+      <c r="B201" s="32">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A202" s="31">
+        <v>201</v>
+      </c>
+      <c r="B202" s="32">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A203" s="31">
+        <v>202</v>
+      </c>
+      <c r="B203" s="32">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A204" s="31">
+        <v>203</v>
+      </c>
+      <c r="B204" s="32">
+        <v>10.199999999999999</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A205" s="31">
+        <v>204</v>
+      </c>
+      <c r="B205" s="32">
+        <v>9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A206" s="31">
+        <v>205</v>
+      </c>
+      <c r="B206" s="32">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A207" s="31">
+        <v>206</v>
+      </c>
+      <c r="B207" s="32">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A208" s="31">
+        <v>207</v>
+      </c>
+      <c r="B208" s="32">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A209" s="31">
+        <v>208</v>
+      </c>
+      <c r="B209" s="32">
+        <v>8.1999999999999993</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A210" s="31">
+        <v>209</v>
+      </c>
+      <c r="B210" s="32">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A211" s="31">
+        <v>210</v>
+      </c>
+      <c r="B211" s="32">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A212" s="31">
+        <v>211</v>
+      </c>
+      <c r="B212" s="32">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A213" s="31">
+        <v>212</v>
+      </c>
+      <c r="B213" s="32">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A214" s="31">
+        <v>213</v>
+      </c>
+      <c r="B214" s="32">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A215" s="31">
+        <v>214</v>
+      </c>
+      <c r="B215" s="32">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A216" s="31">
+        <v>215</v>
+      </c>
+      <c r="B216" s="32">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A217" s="31">
+        <v>216</v>
+      </c>
+      <c r="B217" s="32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A218" s="31">
+        <v>217</v>
+      </c>
+      <c r="B218" s="32">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A219" s="31">
+        <v>218</v>
+      </c>
+      <c r="B219" s="32">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A220" s="31">
+        <v>219</v>
+      </c>
+      <c r="B220" s="32">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A221" s="31">
+        <v>220</v>
+      </c>
+      <c r="B221" s="32">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A222" s="31">
+        <v>221</v>
+      </c>
+      <c r="B222" s="32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A223" s="31">
+        <v>222</v>
+      </c>
+      <c r="B223" s="32">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A224" s="31">
+        <v>223</v>
+      </c>
+      <c r="B224" s="32">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A225" s="31">
+        <v>224</v>
+      </c>
+      <c r="B225" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A226" s="31">
+        <v>225</v>
+      </c>
+      <c r="B226" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A227" s="31">
+        <v>226</v>
+      </c>
+      <c r="B227" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A228" s="31">
+        <v>227</v>
+      </c>
+      <c r="B228" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A229" s="31">
+        <v>228</v>
+      </c>
+      <c r="B229" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A230" s="31">
+        <v>229</v>
+      </c>
+      <c r="B230" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A231" s="31">
+        <v>230</v>
+      </c>
+      <c r="B231" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A232" s="31">
+        <v>231</v>
+      </c>
+      <c r="B232" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A233" s="31">
+        <v>232</v>
+      </c>
+      <c r="B233" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A234" s="31">
+        <v>233</v>
+      </c>
+      <c r="B234" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A235" s="31">
+        <v>234</v>
+      </c>
+      <c r="B235" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A236" s="31">
+        <v>235</v>
+      </c>
+      <c r="B236" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A237" s="31">
+        <v>236</v>
+      </c>
+      <c r="B237" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A238" s="31">
+        <v>237</v>
+      </c>
+      <c r="B238" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A239" s="31">
+        <v>238</v>
+      </c>
+      <c r="B239" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A240" s="31">
+        <v>239</v>
+      </c>
+      <c r="B240" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A241" s="31">
+        <v>240</v>
+      </c>
+      <c r="B241" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A242" s="31">
+        <v>241</v>
+      </c>
+      <c r="B242" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A243" s="31">
+        <v>242</v>
+      </c>
+      <c r="B243" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A244" s="31">
+        <v>243</v>
+      </c>
+      <c r="B244" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A245" s="31">
+        <v>244</v>
+      </c>
+      <c r="B245" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A246" s="31">
+        <v>245</v>
+      </c>
+      <c r="B246" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A247" s="31">
+        <v>246</v>
+      </c>
+      <c r="B247" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A248" s="31">
+        <v>247</v>
+      </c>
+      <c r="B248" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A249" s="31">
+        <v>248</v>
+      </c>
+      <c r="B249" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A250" s="31">
+        <v>249</v>
+      </c>
+      <c r="B250" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A251" s="31">
+        <v>250</v>
+      </c>
+      <c r="B251" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A252" s="31">
+        <v>251</v>
+      </c>
+      <c r="B252" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A253" s="31">
+        <v>252</v>
+      </c>
+      <c r="B253" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A254" s="31">
+        <v>253</v>
+      </c>
+      <c r="B254" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A255" s="31">
+        <v>254</v>
+      </c>
+      <c r="B255" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A256" s="31">
+        <v>255</v>
+      </c>
+      <c r="B256" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A257" s="31">
+        <v>256</v>
+      </c>
+      <c r="B257" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A258" s="31">
+        <v>257</v>
+      </c>
+      <c r="B258" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A259" s="31">
+        <v>258</v>
+      </c>
+      <c r="B259" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A260" s="31">
+        <v>259</v>
+      </c>
+      <c r="B260" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A261" s="31">
+        <v>260</v>
+      </c>
+      <c r="B261" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A262" s="31">
+        <v>261</v>
+      </c>
+      <c r="B262" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A263" s="31">
+        <v>262</v>
+      </c>
+      <c r="B263" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A264" s="31">
+        <v>263</v>
+      </c>
+      <c r="B264" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A265" s="31">
+        <v>264</v>
+      </c>
+      <c r="B265" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A266" s="31">
+        <v>265</v>
+      </c>
+      <c r="B266" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A267" s="31">
+        <v>266</v>
+      </c>
+      <c r="B267" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A268" s="31">
+        <v>267</v>
+      </c>
+      <c r="B268" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A269" s="31">
+        <v>268</v>
+      </c>
+      <c r="B269" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A270" s="31">
+        <v>269</v>
+      </c>
+      <c r="B270" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A271" s="31">
+        <v>270</v>
+      </c>
+      <c r="B271" s="32">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>